--- a/hourly datasets/cap_gen_year-3final.xlsx
+++ b/hourly datasets/cap_gen_year-3final.xlsx
@@ -485,7 +485,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1127464861192516</v>
+        <v>0.1108851287850246</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07426135796710345</v>
+        <v>0.07257018109190863</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +503,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.1870078440863551</v>
+        <v>0.1834553098769333</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07989740725516165</v>
+        <v>0.07876345468679044</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +521,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.1926438933744133</v>
+        <v>0.1896485834718151</v>
       </c>
     </row>
     <row r="5">
@@ -531,15 +531,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05793317263531943</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+        <v>0.05845178300752574</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.006917770544097878</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7.228753303342124</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.06260231366306382</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.04488407132993794</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.07201949468511326</v>
+      </c>
       <c r="H5" t="n">
-        <v>0.1706796587545711</v>
+        <v>0.1693369117925504</v>
       </c>
     </row>
     <row r="6">
@@ -549,25 +559,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04473943535494208</v>
+        <v>0.04661436497509842</v>
       </c>
       <c r="C6" t="n">
-        <v>0.005325043559503317</v>
+        <v>0.004569143740340792</v>
       </c>
       <c r="D6" t="n">
-        <v>3.648885329716293</v>
+        <v>4.255139704226781</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01345280638785308</v>
+        <v>0.0115855717911583</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03425518317390631</v>
+        <v>0.03765102492906399</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05522368753597827</v>
+        <v>0.05557770502113258</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1574859214741937</v>
+        <v>0.1574994937601231</v>
       </c>
     </row>
     <row r="7">
@@ -577,25 +587,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02903735774562823</v>
+        <v>0.03303696888761967</v>
       </c>
       <c r="C7" t="n">
-        <v>0.003044100755573473</v>
+        <v>0.002692971855653346</v>
       </c>
       <c r="D7" t="n">
-        <v>2.139757338538166</v>
+        <v>2.925764722111411</v>
       </c>
       <c r="E7" t="n">
-        <v>5.900886818307892e-05</v>
+        <v>5.779590495100467e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02306212863388198</v>
+        <v>0.02775154842860773</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03501258685737458</v>
+        <v>0.03832238934663149</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1417838438648799</v>
+        <v>0.1439220976726443</v>
       </c>
     </row>
     <row r="8">
@@ -605,25 +615,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02866960613684441</v>
+        <v>0.03267105037729079</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002732353517780752</v>
+        <v>0.002390401883020987</v>
       </c>
       <c r="D8" t="n">
-        <v>2.210747649709623</v>
+        <v>3.045210485321653</v>
       </c>
       <c r="E8" t="n">
-        <v>3.076690044233385e-07</v>
+        <v>1.468695680592761e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02330582168138613</v>
+        <v>0.02797900401437984</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03403339059230218</v>
+        <v>0.03736309674020178</v>
       </c>
       <c r="H8" t="n">
-        <v>0.141416092256096</v>
+        <v>0.1435561791623154</v>
       </c>
     </row>
     <row r="9">
@@ -633,25 +643,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0138662000905528</v>
+        <v>0.01682381381329842</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003605075256054655</v>
+        <v>0.003303825424179423</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005206977931849108</v>
+        <v>0.6471347595543064</v>
       </c>
       <c r="E9" t="n">
-        <v>1.778910002200519e-05</v>
+        <v>1.76784284147458e-05</v>
       </c>
       <c r="F9" t="n">
-        <v>0.006790550059476552</v>
+        <v>0.01034019350137693</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02094185012162898</v>
+        <v>0.02330743412522013</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1266126862098044</v>
+        <v>0.127708942598323</v>
       </c>
     </row>
     <row r="10">
@@ -661,25 +671,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.859951780417363e-05</v>
+        <v>0.00754726494357736</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001127331343166753</v>
+        <v>0.0008692690151991379</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.00913892949151</v>
+        <v>0.3212422767239589</v>
       </c>
       <c r="E10" t="n">
-        <v>1.995100196980731e-07</v>
+        <v>3.427596716604433e-07</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.002198755385376016</v>
+        <v>0.005837130518842777</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002235954420984398</v>
+        <v>0.009257399368311851</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1127650856370558</v>
+        <v>0.118432393728602</v>
       </c>
     </row>
     <row r="11">
@@ -689,7 +699,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02657163319265903</v>
+        <v>0.02726811457713658</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -697,7 +707,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1393181193119107</v>
+        <v>0.1381532433621612</v>
       </c>
     </row>
     <row r="12">
@@ -707,7 +717,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04287082235326538</v>
+        <v>0.04254995080805974</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -715,7 +725,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.155617308472517</v>
+        <v>0.1534350795930844</v>
       </c>
     </row>
     <row r="13">
@@ -725,7 +735,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.0491633941321979</v>
+        <v>0.04718192544185033</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -733,7 +743,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1619098802514495</v>
+        <v>0.1580670542268749</v>
       </c>
     </row>
     <row r="14">
@@ -743,25 +753,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.0514568738883066</v>
+        <v>0.05203835719127433</v>
       </c>
       <c r="C14" t="n">
-        <v>0.008987261085764024</v>
+        <v>0.0084463235480893</v>
       </c>
       <c r="D14" t="n">
-        <v>9.198863409012212</v>
+        <v>9.725559734492517</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0444454659280662</v>
+        <v>0.0415918345581896</v>
       </c>
       <c r="F14" t="n">
-        <v>0.03379007168371145</v>
+        <v>0.03547433291277874</v>
       </c>
       <c r="G14" t="n">
-        <v>0.06912367609290182</v>
+        <v>0.06860238146977003</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1642033600075582</v>
+        <v>0.162923485976299</v>
       </c>
     </row>
     <row r="15">
@@ -771,7 +781,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05828135157323943</v>
+        <v>0.05759145315637489</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -779,7 +789,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1710278376924911</v>
+        <v>0.1684765819413995</v>
       </c>
     </row>
     <row r="16">
@@ -789,25 +799,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0619259653860847</v>
+        <v>0.06075048481185639</v>
       </c>
       <c r="C16" t="n">
-        <v>0.009099232169588472</v>
+        <v>0.008225181909758159</v>
       </c>
       <c r="D16" t="n">
-        <v>9.907563843853747</v>
+        <v>10.44565100464527</v>
       </c>
       <c r="E16" t="n">
-        <v>0.04583561235697588</v>
+        <v>0.04334690651695119</v>
       </c>
       <c r="F16" t="n">
-        <v>0.04404726587570973</v>
+        <v>0.04461990944552154</v>
       </c>
       <c r="G16" t="n">
-        <v>0.07980466489645974</v>
+        <v>0.07688106017819131</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1746724515053363</v>
+        <v>0.171635613596881</v>
       </c>
     </row>
     <row r="17">
@@ -817,25 +827,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.06708972670187829</v>
+        <v>0.06442214283270582</v>
       </c>
       <c r="C17" t="n">
-        <v>0.009059498303894638</v>
+        <v>0.007966533235859751</v>
       </c>
       <c r="D17" t="n">
-        <v>10.28598447811154</v>
+        <v>10.83152295911162</v>
       </c>
       <c r="E17" t="n">
-        <v>0.03945756713915682</v>
+        <v>0.03822612480211291</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0492684602889722</v>
+        <v>0.04879877387327741</v>
       </c>
       <c r="G17" t="n">
-        <v>0.08491099311478427</v>
+        <v>0.08004551179213401</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1798362128211299</v>
+        <v>0.1753072716177305</v>
       </c>
     </row>
     <row r="18">
@@ -845,22 +855,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1127464861192516</v>
+        <v>-0.1108851287850246</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01268551493633767</v>
+        <v>0.01168476278832965</v>
       </c>
       <c r="D18" t="n">
-        <v>-16.06863000417736</v>
+        <v>-17.06156410909713</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01260794727490581</v>
+        <v>0.01465261168374973</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1376583015129513</v>
+        <v>-0.1337989318712714</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.08783467072555183</v>
+        <v>-0.08797132569877801</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -873,25 +883,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.06296001873867402</v>
+        <v>0.06392568488482772</v>
       </c>
       <c r="C19" t="n">
-        <v>0.008772607598267574</v>
+        <v>0.007920605838630794</v>
       </c>
       <c r="D19" t="n">
-        <v>10.12573975635952</v>
+        <v>10.72497835534307</v>
       </c>
       <c r="E19" t="n">
-        <v>0.04611348190673749</v>
+        <v>0.04362681238529957</v>
       </c>
       <c r="F19" t="n">
-        <v>0.04569548489236878</v>
+        <v>0.04839072237781416</v>
       </c>
       <c r="G19" t="n">
-        <v>0.08022455258497924</v>
+        <v>0.07946064739184133</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1757065048579257</v>
+        <v>0.1748108136698523</v>
       </c>
     </row>
     <row r="20">
@@ -901,25 +911,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.06575380948743922</v>
+        <v>0.06493663629790954</v>
       </c>
       <c r="C20" t="n">
-        <v>0.008779186937611547</v>
+        <v>0.008235176616830981</v>
       </c>
       <c r="D20" t="n">
-        <v>10.60119039919291</v>
+        <v>11.17063132604549</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0454350173039485</v>
+        <v>0.04448607005104712</v>
       </c>
       <c r="F20" t="n">
-        <v>0.04853220242406418</v>
+        <v>0.04878281383500075</v>
       </c>
       <c r="G20" t="n">
-        <v>0.08297541655081425</v>
+        <v>0.0810904587608183</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1785002956066908</v>
+        <v>0.1758217650829342</v>
       </c>
     </row>
     <row r="21">
@@ -929,25 +939,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.06845930811803592</v>
+        <v>0.06773892214017871</v>
       </c>
       <c r="C21" t="n">
-        <v>0.009017170268084507</v>
+        <v>0.008166663927919525</v>
       </c>
       <c r="D21" t="n">
-        <v>11.11654896095957</v>
+        <v>11.75738394753627</v>
       </c>
       <c r="E21" t="n">
-        <v>0.04765362754886252</v>
+        <v>0.0453633952453375</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0507228984519586</v>
+        <v>0.05171916504191797</v>
       </c>
       <c r="G21" t="n">
-        <v>0.08619571778411324</v>
+        <v>0.08375867923843948</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1812057942372876</v>
+        <v>0.1786240509252033</v>
       </c>
     </row>
     <row r="22">
@@ -957,25 +967,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.06723363870094134</v>
+        <v>0.06705126583707244</v>
       </c>
       <c r="C22" t="n">
-        <v>0.008570173494798092</v>
+        <v>0.008181773283238304</v>
       </c>
       <c r="D22" t="n">
-        <v>10.64023457573836</v>
+        <v>11.2394804319417</v>
       </c>
       <c r="E22" t="n">
-        <v>0.04404701339746033</v>
+        <v>0.04235292008785945</v>
       </c>
       <c r="F22" t="n">
-        <v>0.05042658461121194</v>
+        <v>0.0510066874543294</v>
       </c>
       <c r="G22" t="n">
-        <v>0.08404069279067078</v>
+        <v>0.08309584421981542</v>
       </c>
       <c r="H22" t="n">
-        <v>0.179980124820193</v>
+        <v>0.1779363946220971</v>
       </c>
     </row>
     <row r="23">
@@ -985,25 +995,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0709451441382204</v>
+        <v>0.0686005431992298</v>
       </c>
       <c r="C23" t="n">
-        <v>0.009136867550119877</v>
+        <v>0.007968186373272922</v>
       </c>
       <c r="D23" t="n">
-        <v>10.86079618772808</v>
+        <v>11.41698709553015</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04601868827903455</v>
+        <v>0.04467330313635892</v>
       </c>
       <c r="F23" t="n">
-        <v>0.05296322388597911</v>
+        <v>0.05297510127857574</v>
       </c>
       <c r="G23" t="n">
-        <v>0.08892706439046179</v>
+        <v>0.08422598511988377</v>
       </c>
       <c r="H23" t="n">
-        <v>0.183691630257472</v>
+        <v>0.1794856719842544</v>
       </c>
     </row>
     <row r="24">
@@ -1013,25 +1023,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.06880958640594251</v>
+        <v>0.06938490394795829</v>
       </c>
       <c r="C24" t="n">
-        <v>0.008419400757893004</v>
+        <v>0.008019650441525241</v>
       </c>
       <c r="D24" t="n">
-        <v>10.97351591077867</v>
+        <v>11.55835663155765</v>
       </c>
       <c r="E24" t="n">
-        <v>0.04762091744852344</v>
+        <v>0.04727088213598934</v>
       </c>
       <c r="F24" t="n">
-        <v>0.05228936199531305</v>
+        <v>0.05365914925220614</v>
       </c>
       <c r="G24" t="n">
-        <v>0.08532981081657202</v>
+        <v>0.08511065864371054</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1815560725251941</v>
+        <v>0.1802700327329829</v>
       </c>
     </row>
     <row r="25">
@@ -1041,25 +1051,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.07205723425062011</v>
+        <v>0.06965000327254312</v>
       </c>
       <c r="C25" t="n">
-        <v>0.009293694449334101</v>
+        <v>0.008023364588327947</v>
       </c>
       <c r="D25" t="n">
-        <v>11.22572366810779</v>
+        <v>11.76386248192458</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05517921973289089</v>
+        <v>0.05298696110130749</v>
       </c>
       <c r="F25" t="n">
-        <v>0.05373720482041149</v>
+        <v>0.05391630656664189</v>
       </c>
       <c r="G25" t="n">
-        <v>0.09037726368082857</v>
+        <v>0.08538369997844428</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1848037203698717</v>
+        <v>0.1805351320575677</v>
       </c>
     </row>
     <row r="26">
@@ -1069,25 +1079,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.07028253204454092</v>
+        <v>0.07030469727479326</v>
       </c>
       <c r="C26" t="n">
-        <v>0.008480875819898617</v>
+        <v>0.008110116216667386</v>
       </c>
       <c r="D26" t="n">
-        <v>11.25509295538604</v>
+        <v>11.72741846473421</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06387091180657176</v>
+        <v>0.0625646364156537</v>
       </c>
       <c r="F26" t="n">
-        <v>0.05365321403214315</v>
+        <v>0.05440295647306601</v>
       </c>
       <c r="G26" t="n">
-        <v>0.08691185005693863</v>
+        <v>0.0862064380765207</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1830290181637926</v>
+        <v>0.1811898260598179</v>
       </c>
     </row>
     <row r="27">
@@ -1097,25 +1107,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.07370065546307279</v>
+        <v>0.0721928516108379</v>
       </c>
       <c r="C27" t="n">
-        <v>0.008935302678955991</v>
+        <v>0.00823746102125528</v>
       </c>
       <c r="D27" t="n">
-        <v>10.84867078324668</v>
+        <v>11.39218018904227</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06086329690069334</v>
+        <v>0.05754044370118</v>
       </c>
       <c r="F27" t="n">
-        <v>0.05615715177024259</v>
+        <v>0.05603545348844155</v>
       </c>
       <c r="G27" t="n">
-        <v>0.09124415915590282</v>
+        <v>0.08835024973323422</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1864471415823244</v>
+        <v>0.1830779803958625</v>
       </c>
     </row>
     <row r="28">
@@ -1125,25 +1135,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.07264075851552446</v>
+        <v>0.07087438025342341</v>
       </c>
       <c r="C28" t="n">
-        <v>0.008723775816604214</v>
+        <v>0.008016087067954524</v>
       </c>
       <c r="D28" t="n">
-        <v>10.75418622437872</v>
+        <v>11.32108815481675</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08402750342740545</v>
+        <v>0.08490309173276107</v>
       </c>
       <c r="F28" t="n">
-        <v>0.05551770485459395</v>
+        <v>0.05515504398961084</v>
       </c>
       <c r="G28" t="n">
-        <v>0.08976381217645463</v>
+        <v>0.08659371651723594</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1853872446347761</v>
+        <v>0.181759509038448</v>
       </c>
     </row>
     <row r="29">
@@ -1153,25 +1163,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.003941038007569537</v>
+        <v>0.006496218918767228</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0014940422368962</v>
+        <v>0.0008000687582302823</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7128851805879993</v>
+        <v>0.2665443996571934</v>
       </c>
       <c r="E29" t="n">
-        <v>8.332458489466942e-05</v>
+        <v>2.691122572057404e-05</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0009777423951667277</v>
+        <v>0.004921221231619667</v>
       </c>
       <c r="G29" t="n">
-        <v>0.006904333619972322</v>
+        <v>0.008071216605914698</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1166875241268212</v>
+        <v>0.1173813477037919</v>
       </c>
     </row>
   </sheetData>

--- a/hourly datasets/cap_gen_year-3final.xlsx
+++ b/hourly datasets/cap_gen_year-3final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_iter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>coef_pos</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.2280165137431313</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -485,7 +490,10 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1108851287850246</v>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1067378182817654</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +503,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07257018109190863</v>
+        <v>0.3318929417789432</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +511,10 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.1834553098769333</v>
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.2106142463175774</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +524,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07876345468679044</v>
+        <v>0.3262279442293795</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +532,10 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.1896485834718151</v>
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2049492487680137</v>
       </c>
     </row>
     <row r="5">
@@ -531,25 +545,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05845178300752574</v>
+        <v>0.3384469971819825</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006917770544097878</v>
+        <v>0.00693183105333385</v>
       </c>
       <c r="D5" t="n">
-        <v>7.228753303342124</v>
+        <v>7.243445891357047</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06260231366306382</v>
+        <v>0.06272955413798874</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04488407132993794</v>
+        <v>0.04497529911719391</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07201949468511326</v>
+        <v>0.07216587577187163</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1693369117925504</v>
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2171683017206166</v>
       </c>
     </row>
     <row r="6">
@@ -559,25 +576,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04661436497509842</v>
+        <v>0.3256220574035727</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004569143740340792</v>
+        <v>0.01105326268094117</v>
       </c>
       <c r="D6" t="n">
-        <v>4.255139704226781</v>
+        <v>11.24368963480012</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0115855717911583</v>
+        <v>0.01224412235132573</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03765102492906399</v>
+        <v>0.101498450191759</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05557770502113258</v>
+        <v>0.1448482201392707</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1574994937601231</v>
+        <v>19</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2043433619422069</v>
       </c>
     </row>
     <row r="7">
@@ -587,25 +607,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03303696888761967</v>
+        <v>0.3344704976249805</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002692971855653346</v>
+        <v>0.01048698818714128</v>
       </c>
       <c r="D7" t="n">
-        <v>2.925764722111411</v>
+        <v>12.26237794790298</v>
       </c>
       <c r="E7" t="n">
-        <v>5.779590495100467e-05</v>
+        <v>6.627173107540521e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02775154842860773</v>
+        <v>0.1080278549220939</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03832238934663149</v>
+        <v>0.1491565232853689</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1439220976726443</v>
+        <v>19</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2131918021636147</v>
       </c>
     </row>
     <row r="8">
@@ -615,25 +638,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03267105037729079</v>
+        <v>0.3383789995128739</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002390401883020987</v>
+        <v>0.01032140906355147</v>
       </c>
       <c r="D8" t="n">
-        <v>3.045210485321653</v>
+        <v>13.12770487986169</v>
       </c>
       <c r="E8" t="n">
-        <v>1.468695680592761e-07</v>
+        <v>2.17827683452014e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02797900401437984</v>
+        <v>0.1149559603055979</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03736309674020178</v>
+        <v>0.15543554253008</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1435561791623154</v>
+        <v>19</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.217100304051508</v>
       </c>
     </row>
     <row r="9">
@@ -643,25 +669,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01682381381329842</v>
+        <v>0.3464191723050098</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003303825424179423</v>
+        <v>0.02530782269378012</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6471347595543064</v>
+        <v>3.924789053148023</v>
       </c>
       <c r="E9" t="n">
-        <v>1.76784284147458e-05</v>
+        <v>0.0001637964505768241</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01034019350137693</v>
+        <v>0.05032048363699538</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02330743412522013</v>
+        <v>0.1495566018207891</v>
       </c>
       <c r="H9" t="n">
-        <v>0.127708942598323</v>
+        <v>19</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.225140476843644</v>
       </c>
     </row>
     <row r="10">
@@ -671,25 +700,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00754726494357736</v>
+        <v>0.338389815664575</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0008692690151991379</v>
+        <v>0.009478779181022839</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3212422767239589</v>
+        <v>4.569721308375848</v>
       </c>
       <c r="E10" t="n">
-        <v>3.427596716604433e-07</v>
+        <v>8.737163307166983e-06</v>
       </c>
       <c r="F10" t="n">
-        <v>0.005837130518842777</v>
+        <v>0.02812259967759572</v>
       </c>
       <c r="G10" t="n">
-        <v>0.009257399368311851</v>
+        <v>0.06529999261082768</v>
       </c>
       <c r="H10" t="n">
-        <v>0.118432393728602</v>
+        <v>51</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.2171111202032092</v>
       </c>
     </row>
     <row r="11">
@@ -699,7 +731,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02726811457713658</v>
+        <v>0.269759177988725</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -707,7 +739,10 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1381532433621612</v>
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1484804825273592</v>
       </c>
     </row>
     <row r="12">
@@ -717,7 +752,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.04254995080805974</v>
+        <v>0.2922723071776833</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -725,7 +760,10 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1534350795930844</v>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1709936117163175</v>
       </c>
     </row>
     <row r="13">
@@ -735,7 +773,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04718192544185033</v>
+        <v>0.2999385959216809</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -743,7 +781,10 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1580670542268749</v>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.178659900460315</v>
       </c>
     </row>
     <row r="14">
@@ -753,25 +794,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05203835719127433</v>
+        <v>0.3067484634723345</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0084463235480893</v>
+        <v>0.00843901217219163</v>
       </c>
       <c r="D14" t="n">
-        <v>9.725559734492517</v>
+        <v>9.719533553306285</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0415918345581896</v>
+        <v>0.04157379587532875</v>
       </c>
       <c r="F14" t="n">
-        <v>0.03547433291277874</v>
+        <v>0.0354147508054496</v>
       </c>
       <c r="G14" t="n">
-        <v>0.06860238146977003</v>
+        <v>0.06851412423588474</v>
       </c>
       <c r="H14" t="n">
-        <v>0.162923485976299</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1854697680109686</v>
       </c>
     </row>
     <row r="15">
@@ -781,7 +825,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05759145315637489</v>
+        <v>0.3137360170097979</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -789,7 +833,10 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1684765819413995</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.192457321548432</v>
       </c>
     </row>
     <row r="16">
@@ -799,25 +846,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06075048481185639</v>
+        <v>0.3178486547519928</v>
       </c>
       <c r="C16" t="n">
-        <v>0.008225181909758159</v>
+        <v>0.008223694565169302</v>
       </c>
       <c r="D16" t="n">
-        <v>10.44565100464527</v>
+        <v>10.44439177652896</v>
       </c>
       <c r="E16" t="n">
-        <v>0.04334690651695119</v>
+        <v>0.0433362501423708</v>
       </c>
       <c r="F16" t="n">
-        <v>0.04461990944552154</v>
+        <v>0.04461079470197718</v>
       </c>
       <c r="G16" t="n">
-        <v>0.07688106017819131</v>
+        <v>0.07686611018909745</v>
       </c>
       <c r="H16" t="n">
-        <v>0.171635613596881</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.196569959290627</v>
       </c>
     </row>
     <row r="17">
@@ -827,25 +877,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.06442214283270582</v>
+        <v>0.3211931654634089</v>
       </c>
       <c r="C17" t="n">
-        <v>0.007966533235859751</v>
+        <v>0.0079649350717428</v>
       </c>
       <c r="D17" t="n">
-        <v>10.83152295911162</v>
+        <v>10.8300794694707</v>
       </c>
       <c r="E17" t="n">
-        <v>0.03822612480211291</v>
+        <v>0.03821666565203539</v>
       </c>
       <c r="F17" t="n">
-        <v>0.04879877387327741</v>
+        <v>0.04878781804683709</v>
       </c>
       <c r="G17" t="n">
-        <v>0.08004551179213401</v>
+        <v>0.08002828594630568</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1753072716177305</v>
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1999144700020431</v>
       </c>
     </row>
     <row r="18">
@@ -855,24 +908,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1108851287850246</v>
+        <v>0.1212786954613658</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01168476278832965</v>
+        <v>0.0115984911181443</v>
       </c>
       <c r="D18" t="n">
-        <v>-17.06156410909713</v>
+        <v>-16.72895783163692</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01465261168374973</v>
+        <v>0.01460193887620047</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1337989318712714</v>
+        <v>-0.1320554012088252</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.08797132569877801</v>
+        <v>-0.08656611897976572</v>
       </c>
       <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -883,25 +939,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.06392568488482772</v>
+        <v>0.3219084270585566</v>
       </c>
       <c r="C19" t="n">
-        <v>0.007920605838630794</v>
+        <v>0.00791867302198202</v>
       </c>
       <c r="D19" t="n">
-        <v>10.72497835534307</v>
+        <v>10.7230998560246</v>
       </c>
       <c r="E19" t="n">
-        <v>0.04362681238529957</v>
+        <v>0.04361682143183036</v>
       </c>
       <c r="F19" t="n">
-        <v>0.04839072237781416</v>
+        <v>0.04837803783988068</v>
       </c>
       <c r="G19" t="n">
-        <v>0.07946064739184133</v>
+        <v>0.07944037735988844</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1748108136698523</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.2006297315971908</v>
       </c>
     </row>
     <row r="20">
@@ -911,25 +970,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.06493663629790954</v>
+        <v>0.3223363787449905</v>
       </c>
       <c r="C20" t="n">
-        <v>0.008235176616830981</v>
+        <v>0.008232776187320151</v>
       </c>
       <c r="D20" t="n">
-        <v>11.17063132604549</v>
+        <v>11.16781917155231</v>
       </c>
       <c r="E20" t="n">
-        <v>0.04448607005104712</v>
+        <v>0.04447164177136281</v>
       </c>
       <c r="F20" t="n">
-        <v>0.04878281383500075</v>
+        <v>0.04876920504066726</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0810904587608183</v>
+        <v>0.08106742564881132</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1758217650829342</v>
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2010576832836247</v>
       </c>
     </row>
     <row r="21">
@@ -939,25 +1001,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.06773892214017871</v>
+        <v>0.3242351666056664</v>
       </c>
       <c r="C21" t="n">
-        <v>0.008166663927919525</v>
+        <v>0.008162064762175406</v>
       </c>
       <c r="D21" t="n">
-        <v>11.75738394753627</v>
+        <v>11.75119920224028</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0453633952453375</v>
+        <v>0.04533000664055415</v>
       </c>
       <c r="F21" t="n">
-        <v>0.05171916504191797</v>
+        <v>0.05168748834687351</v>
       </c>
       <c r="G21" t="n">
-        <v>0.08375867923843948</v>
+        <v>0.08370895764117281</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1786240509252033</v>
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2029564711443005</v>
       </c>
     </row>
     <row r="22">
@@ -967,25 +1032,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.06705126583707244</v>
+        <v>0.3249641990381131</v>
       </c>
       <c r="C22" t="n">
-        <v>0.008181773283238304</v>
+        <v>0.008173822835497498</v>
       </c>
       <c r="D22" t="n">
-        <v>11.2394804319417</v>
+        <v>11.22711554067577</v>
       </c>
       <c r="E22" t="n">
-        <v>0.04235292008785945</v>
+        <v>0.04230705446446077</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0510066874543294</v>
+        <v>0.05094100825976626</v>
       </c>
       <c r="G22" t="n">
-        <v>0.08309584421981542</v>
+        <v>0.08299897213796731</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1779363946220971</v>
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2036855035767473</v>
       </c>
     </row>
     <row r="23">
@@ -995,25 +1063,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0686005431992298</v>
+        <v>0.327092518712376</v>
       </c>
       <c r="C23" t="n">
-        <v>0.007968186373272922</v>
+        <v>0.007959759686559389</v>
       </c>
       <c r="D23" t="n">
-        <v>11.41698709553015</v>
+        <v>11.40356910192141</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04467330313635892</v>
+        <v>0.04465402294761011</v>
       </c>
       <c r="F23" t="n">
-        <v>0.05297510127857574</v>
+        <v>0.05290214110887712</v>
       </c>
       <c r="G23" t="n">
-        <v>0.08422598511988377</v>
+        <v>0.0841199637123147</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1794856719842544</v>
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2058138232510102</v>
       </c>
     </row>
     <row r="24">
@@ -1023,25 +1094,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.06938490394795829</v>
+        <v>0.3287929745852686</v>
       </c>
       <c r="C24" t="n">
-        <v>0.008019650441525241</v>
+        <v>0.008009703089338054</v>
       </c>
       <c r="D24" t="n">
-        <v>11.55835663155765</v>
+        <v>11.54173949215673</v>
       </c>
       <c r="E24" t="n">
-        <v>0.04727088213598934</v>
+        <v>0.04717946779785778</v>
       </c>
       <c r="F24" t="n">
-        <v>0.05365914925220614</v>
+        <v>0.05356611552136768</v>
       </c>
       <c r="G24" t="n">
-        <v>0.08511065864371054</v>
+        <v>0.08497860288707272</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1802700327329829</v>
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2075142791239027</v>
       </c>
     </row>
     <row r="25">
@@ -1051,25 +1125,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.06965000327254312</v>
+        <v>0.3293349950081736</v>
       </c>
       <c r="C25" t="n">
-        <v>0.008023364588327947</v>
+        <v>0.008012881907674929</v>
       </c>
       <c r="D25" t="n">
-        <v>11.76386248192458</v>
+        <v>11.73886078610153</v>
       </c>
       <c r="E25" t="n">
-        <v>0.05298696110130749</v>
+        <v>0.05282100544543662</v>
       </c>
       <c r="F25" t="n">
-        <v>0.05391630656664189</v>
+        <v>0.05378747115397791</v>
       </c>
       <c r="G25" t="n">
-        <v>0.08538369997844428</v>
+        <v>0.08521374515451273</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1805351320575677</v>
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2080562995468078</v>
       </c>
     </row>
     <row r="26">
@@ -1079,25 +1156,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.07030469727479326</v>
+        <v>0.3300315568824053</v>
       </c>
       <c r="C26" t="n">
-        <v>0.008110116216667386</v>
+        <v>0.008096938160210196</v>
       </c>
       <c r="D26" t="n">
-        <v>11.72741846473421</v>
+        <v>11.69615749731426</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0625646364156537</v>
+        <v>0.0620900764770785</v>
       </c>
       <c r="F26" t="n">
-        <v>0.05440295647306601</v>
+        <v>0.05424355261825543</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0862064380765207</v>
+        <v>0.08599534415823031</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1811898260598179</v>
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2087528614210394</v>
       </c>
     </row>
     <row r="27">
@@ -1107,25 +1187,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0721928516108379</v>
+        <v>0.3319784308222211</v>
       </c>
       <c r="C27" t="n">
-        <v>0.00823746102125528</v>
+        <v>0.008221228523409755</v>
       </c>
       <c r="D27" t="n">
-        <v>11.39218018904227</v>
+        <v>11.3538524512429</v>
       </c>
       <c r="E27" t="n">
-        <v>0.05754044370118</v>
+        <v>0.05714892840632448</v>
       </c>
       <c r="F27" t="n">
-        <v>0.05603545348844155</v>
+        <v>0.0558434200150812</v>
       </c>
       <c r="G27" t="n">
-        <v>0.08835024973323422</v>
+        <v>0.08809452977162406</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1830779803958625</v>
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2106997353608553</v>
       </c>
     </row>
     <row r="28">
@@ -1135,25 +1218,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.07087438025342341</v>
+        <v>0.3296341621877785</v>
       </c>
       <c r="C28" t="n">
-        <v>0.008016087067954524</v>
+        <v>0.007995119582320796</v>
       </c>
       <c r="D28" t="n">
-        <v>11.32108815481675</v>
+        <v>11.27355498357326</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08490309173276107</v>
+        <v>0.08428264826451032</v>
       </c>
       <c r="F28" t="n">
-        <v>0.05515504398961084</v>
+        <v>0.05491117569600157</v>
       </c>
       <c r="G28" t="n">
-        <v>0.08659371651723594</v>
+        <v>0.0862675828995683</v>
       </c>
       <c r="H28" t="n">
-        <v>0.181759509038448</v>
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2083554667264127</v>
       </c>
     </row>
     <row r="29">
@@ -1163,25 +1249,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.006496218918767228</v>
+        <v>0.3287514227609108</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0008000687582302823</v>
+        <v>0.009417387568833445</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2665443996571934</v>
+        <v>3.521824451151482</v>
       </c>
       <c r="E29" t="n">
-        <v>2.691122572057404e-05</v>
+        <v>0.0006861800422604804</v>
       </c>
       <c r="F29" t="n">
-        <v>0.004921221231619667</v>
+        <v>0.01818572623003305</v>
       </c>
       <c r="G29" t="n">
-        <v>0.008071216605914698</v>
+        <v>0.05512379576834966</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1173813477037919</v>
+        <v>51</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.207472727299545</v>
       </c>
     </row>
   </sheetData>
